--- a/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
+++ b/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Work sheets: Entries (tasks 1–2), Schedule (tasks 5–6, 9, 13), Beds (7), Q15 Log (8), Admissions (10), Supplies and Order (11), Roster (12), and Clinic Grid (bonus).</t>
+          <t>Where to work: Entries (tasks 1–2), the Practice sheet itself (3–4), Schedule (5–6, 9, 13), Beds (7), Q15 Log (8), Admissions (10), Supplies and Order (11), Roster (12), and Clinic Grid (bonus).</t>
         </is>
       </c>
     </row>
@@ -1095,6 +1095,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,10 +1174,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="64" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Julie Osei, MD, at the Primary Care Clinic in the Bluestone Outpatient Pavilion, needs an appointment template for the two weeks of Monday 01/05/2026 through Friday 01/16/2026. The clinic books 15-minute slots from 08:00 to 16:45 on weekdays only. Lunch (12:00–12:45) is blocked every day, Wednesday afternoons (13:00 onward) are admin time, and Friday afternoons become video visits. Build the whole grid on the Clinic Grid sheet with AutoFill, Fill Series, Ctrl+Enter, and Find &amp; Replace, without typing cell by cell. B3 (01/05/2026) and A4 (08:00) are filled in for you.</t>
+          <t>Julie Osei, MD, at the Primary Care Clinic in the Bluestone Outpatient Pavilion, needs an appointment template for the two weeks of Monday 01/05/2026 through Friday 01/16/2026. The clinic books 15-minute slots from 08:00 to 16:45 on weekdays only. Lunch (12:00–12:45) is blocked every day, Wednesday afternoons (13:00 onward) are admin time, and Friday afternoons become video visits. Build the whole grid on the Clinic Grid sheet with AutoFill, Fill Series, Ctrl+Enter, and Find &amp; Replace, without typing cell by cell. B3 (01/05/2026) and A4 (08:00) are filled in for you. The first four parts are checked by gray cells that read the Clinic Grid, so don't type over them. The last part has a yellow cell for your answer.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1271,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="81" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
           <t>B3</t>
@@ -1248,7 +1279,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. How many slots are blocked (Lunch plus Admin)? The gray cell counts blocks in the right places, minus any in the wrong place.</t>
+          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1265,7 +1296,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="66" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B4</t>
@@ -1273,7 +1304,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Select both Friday-afternoon blocks (13:00–16:45), then use Find &amp; Replace to change Open to Telehealth inside that selection only. How many replacements does Excel report? The gray cell counts Telehealth slots in the right places.</t>
+          <t>Select both Friday-afternoon blocks (13:00–16:45), then use Find &amp; Replace to change Open to Telehealth inside that selection only. Excel reports how many replacements it made. The gray cell counts Telehealth slots in the right places, minus any in the wrong place, so the two numbers should agree.</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1290,7 +1321,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="51" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -1298,7 +1329,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>After all the steps above, how many slots are still Open for in-person booking? The gray cell counts them.</t>
+          <t>How many slots are still Open for in-person booking? Work it out from the size of the grid and the slots you blocked or converted, then confirm it on the Clinic Grid with Find All. Type the number in the yellow cell.</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -1306,10 +1337,7 @@
           <t>Total slots minus everything you blocked or converted</t>
         </is>
       </c>
-      <c r="D10" cm="1" s="28">
-        <f t="array" ref="D10">IF(COUNTA('Clinic Grid'!B4:K39)=0,"",COUNTIF('Clinic Grid'!B4:K39,"Open"))</f>
-        <v/>
-      </c>
+      <c r="D10" s="21" t="n"/>
       <c r="E10" s="22">
         <f>IF(IFERROR(D10="",FALSE),"",IF(IFERROR(AND(ISNUMBER(D10),OR(ABS(D10-'Bonus Key'!$C$9)&lt;=0.0001)),FALSE),"✔ Correct","✘ Not yet"))</f>
         <v/>
@@ -1969,7 +1997,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Entries!B7 shows the ED arrival as a date and time. What number does Excel actually store in that cell? Switch the cell to General format to see it, and enter it rounded to 2 decimal places.</t>
+          <t>Entries!B7 shows the ED arrival as a date and time. What number does Excel actually store in that cell? Switch the cell to General format to see it, then type that number in the yellow cell, rounded to 2 decimal places.</t>
         </is>
       </c>
       <c r="C6" s="59" t="n">
@@ -2091,7 +2119,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>B5 holds "Mon". Fill the weekday names down to B35 by double-clicking the fill handle instead of dragging. The gray cell shows the day name in B35.</t>
+          <t>On the Schedule sheet, B5 holds "Mon". Fill the weekday names down to B35 by double-clicking the fill handle instead of dragging. The gray cell shows the day name in B35.</t>
         </is>
       </c>
       <c r="C10" s="57" t="inlineStr">
@@ -2173,7 +2201,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>Times are fractions of a day, so 15 minutes is 0:15 (0.0104…). The Series dialog adds that step until it reaches the Stop value. A stop of 18:50 rather than 18:45 protects you from tiny rounding errors that can drop the last time. With two starting cells, AutoFill copies the gap between them. Either way you get 48 check times. A single time dragged on its own steps by a whole hour, not 15 minutes.</t>
+          <t>Times are fractions of a day, so 15 minutes is 0:15 (0.0104…). The Fill Series dialog adds that step until it reaches the Stop value. A stop of 18:50 rather than 18:45 protects you from tiny rounding errors that can drop the last time. With two starting cells, AutoFill copies the gap between them. Either way you get 48 check times. A single time dragged on its own steps by a whole hour, not 15 minutes.</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2213,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Float RN column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
+          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
         </is>
       </c>
       <c r="C13" s="57" t="n">
@@ -2476,7 +2504,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. How many slots are blocked (Lunch plus Admin)? The gray cell counts blocks in the right places, minus any in the wrong place.</t>
+          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
         </is>
       </c>
       <c r="C7" s="57" t="n">
@@ -2508,7 +2536,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Select both Friday-afternoon blocks (13:00–16:45), then use Find &amp; Replace to change Open to Telehealth inside that selection only. How many replacements does Excel report? The gray cell counts Telehealth slots in the right places.</t>
+          <t>Select both Friday-afternoon blocks (13:00–16:45), then use Find &amp; Replace to change Open to Telehealth inside that selection only. Excel reports how many replacements it made. The gray cell counts Telehealth slots in the right places, minus any in the wrong place, so the two numbers should agree.</t>
         </is>
       </c>
       <c r="C8" s="57" t="n">
@@ -2532,7 +2560,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1">
+    <row r="9" ht="111" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>B5</t>
@@ -2540,7 +2568,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>After all the steps above, how many slots are still Open for in-person booking? The gray cell counts them.</t>
+          <t>How many slots are still Open for in-person booking? Work it out from the size of the grid and the slots you blocked or converted, then confirm it on the Clinic Grid with Find All. Type the number in the yellow cell.</t>
         </is>
       </c>
       <c r="C9" s="57" t="n">
@@ -2548,7 +2576,7 @@
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>No new steps: the gray cell counts the cells that still say Open.</t>
+          <t>Work it out: 36 rows × 10 days = 360 slots, minus 40 Lunch, 32 Admin, and 32 Telehealth = **256**. To confirm, click one cell on the Clinic Grid, press **Ctrl + F** (Mac: **⌃ + F**), type `Open`, tick **Match entire cell contents**, and click **Find All**. The dialog reports *"256 cell(s) found"*.</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -2558,7 +2586,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>360 slots − 40 Lunch − 32 Admin − 32 Telehealth = 256. If your count is higher, part of a block is missing. If it's lower, something extra was overwritten.</t>
+          <t>Lunch takes 4 slots on each of 10 days (40). Admin and Telehealth each take the 16 afternoon slots on 2 days (32 and 32). That leaves 360 − 40 − 32 − 32 = 256 Open slots. If Find All reports more, part of a block is missing. If it reports fewer, something extra was overwritten. Working the number out first and then counting is a quick way to catch a fill that went wrong.</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2626,7 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Most tasks are done on the other sheets (Entries, Schedule, Q15 Log, Beds, Admissions, Supplies, Order, Roster). Type in the yellow cells here. A gray cell is a pre-filled formula that reads your work on another sheet, and its Check turns green when that work is right. Do the tasks in order, because the Schedule tasks build on each other.</t>
+          <t>Most tasks are done on the other sheets (Entries, Schedule, Beds, Q15 Log, Admissions, Supplies, Order, Roster). Type in the yellow cells here. A gray cell is a pre-filled formula that reads your work on another sheet, and its Check turns green when that work is right. Do the tasks in order, because the Schedule tasks build on each other.</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Entries!B7 shows the ED arrival as a date and time. What number does Excel actually store in that cell? Switch the cell to General format to see it, and enter it rounded to 2 decimal places.</t>
+          <t>Entries!B7 shows the ED arrival as a date and time. What number does Excel actually store in that cell? Switch the cell to General format to see it, then type that number in the yellow cell, rounded to 2 decimal places.</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -2755,7 +2783,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
           <t>6</t>
@@ -2763,7 +2791,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>B5 holds "Mon". Fill the weekday names down to B35 by double-clicking the fill handle instead of dragging. The gray cell shows the day name in B35.</t>
+          <t>On the Schedule sheet, B5 holds "Mon". Fill the weekday names down to B35 by double-clicking the fill handle instead of dragging. The gray cell shows the day name in B35.</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2838,7 +2866,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Float RN column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
+          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2868,7 +2896,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Type an example that can only mean one thing, then press Ctrl + E</t>
+          <t>Type an example that can only mean one thing, then press Ctrl + E (Mac: Data → Flash Fill)</t>
         </is>
       </c>
       <c r="D15" cm="1" s="28">
@@ -3325,7 +3353,7 @@
       </c>
       <c r="O4" s="38" t="inlineStr">
         <is>
-          <t>Float RN</t>
+          <t>Weekend float</t>
         </is>
       </c>
     </row>

--- a/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
+++ b/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -355,16 +355,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -918,7 +915,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="B16" s="8" t="inlineStr">
         <is>
           <t>3. Check yourself</t>
@@ -926,7 +923,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red). Tasks marked 'See key' are checked by comparing with the answer key.</t>
+          <t>The Check column shows ✔ Correct (green) or ✘ Not yet (red).</t>
         </is>
       </c>
     </row>
@@ -994,7 +991,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Pre-filled summary formula — it reads the work you did on another sheet.</t>
+          <t>Pre-filled summary formula. It reads the work you did on another sheet, so don't type over it.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1015,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Not matching yet — check the hint and try again.</t>
+          <t>Not matching yet. Check the hint and try again.</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1035,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 14 rows — Excel Table 'tblSupplies'</t>
+          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1047,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows — Excel Table 'tblAdmissions'</t>
+          <t>Data: 24 rows, in the Excel Table 'tblAdmissions'</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1904,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1921,7 +1918,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -1973,8 +1970,8 @@
       </c>
       <c r="D5" s="58" t="inlineStr">
         <is>
-          <t>1. Select **Entries!B4:B15**.
-2. Right-click the status bar and tick **Numerical Count** if it isn't showing.
+          <t>1. Select Entries!B4:B15.
+2. Right-click the status bar and tick Numerical Count if it isn't showing.
 3. Read Numerical Count (Count shows 12, because it counts every non-empty cell).</t>
         </is>
       </c>
@@ -2005,7 +2002,7 @@
       </c>
       <c r="D6" s="58" t="inlineStr">
         <is>
-          <t>Select **Entries!B7** and press **Ctrl + Shift + ~** (Mac: **⌃ + Shift + ~**), or choose **Home → Number Format → General**. Read the number, then press **Ctrl + Z** (Mac: **⌘ + Z**) to put the date format back.</t>
+          <t>Select Entries!B7 and press Ctrl + Shift + ~ (Mac: ⌃ + Shift + ~), or choose Home → Number Format → General. Read the number, then press Ctrl + Z (Mac: ⌘ + Z) to put the date format back.</t>
         </is>
       </c>
       <c r="E6" cm="1" s="60">
@@ -2036,16 +2033,16 @@
       </c>
       <c r="D7" s="58" t="inlineStr">
         <is>
-          <t>Type **'00393694** (start with an apostrophe) and press **Enter**. The apostrophe tells Excel "this is text" and is not shown in the cell.</t>
-        </is>
-      </c>
-      <c r="E7" cm="1" s="61">
+          <t>Type '00393694 (start with an apostrophe) and press Enter. The apostrophe tells Excel "this is text" and is not shown in the cell.</t>
+        </is>
+      </c>
+      <c r="E7" cm="1" s="19">
         <f t="array" ref="E7">TEXT(Entries!B5,"00000000")</f>
         <v/>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>Typed plainly, 00393694 becomes the number 393694, because numbers don't have leading zeros. An apostrophe (or formatting the cell as Text *before* you type) stores the characters exactly as typed. A custom number format like 00000000 only *displays* zeros on top of the number, so the stored value would still be wrong for matching and lookups. (The live formula in the key rebuilds the text with TEXT, which you'll meet in Lesson 2.2.)</t>
+          <t>Typed plainly, 00393694 becomes the number 393694, because numbers don't have leading zeros. An apostrophe (or formatting the cell as Text before you type) stores the characters exactly as typed. A custom number format like 00000000 only displays zeros on top of the number, so the stored value would still be wrong for matching and lookups. (The live formula in the key rebuilds the text with TEXT, which you'll meet in Lesson 2.2.)</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2065,7 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>Type `Allergy: Penicillin`, press **Alt + Enter** (Mac: **⌃ + ⌥ + Return**), type `Isolation: Contact`, then press **Enter**.</t>
+          <t>Type Allergy: Penicillin, press Alt + Enter (Mac: ⌃ + ⌥ + Return), type Isolation: Contact, then press Enter.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2093,15 +2090,15 @@
           <t>On the Schedule sheet, A5 holds 12/01/2025. Use the fill handle to fill the yellow cells A6:A35 with the rest of December, one day per row. The gray cell shows your last date.</t>
         </is>
       </c>
-      <c r="C9" s="62" t="n">
+      <c r="C9" s="61" t="n">
         <v>46022</v>
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>Select **A5**, point at the fill handle (the small square at its bottom-right corner) until the pointer becomes a thin **+**, and drag down to **A35**.</t>
-        </is>
-      </c>
-      <c r="E9" cm="1" s="63">
+          <t>Select A5, point at the fill handle (the small square at its bottom-right corner) until the pointer becomes a thin +, and drag down to A35.</t>
+        </is>
+      </c>
+      <c r="E9" cm="1" s="62">
         <f t="array" ref="E9">Schedule!A5+30</f>
         <v/>
       </c>
@@ -2129,10 +2126,10 @@
       </c>
       <c r="D10" s="58" t="inlineStr">
         <is>
-          <t>Select **B5** and **double-click** its fill handle. Excel fills down as far as the dates in the neighboring column A go.</t>
-        </is>
-      </c>
-      <c r="E10" cm="1" s="61">
+          <t>Select B5 and double-click its fill handle. Excel fills down as far as the dates in the neighboring column A go.</t>
+        </is>
+      </c>
+      <c r="E10" cm="1" s="19">
         <f t="array" ref="E10">TEXT(Schedule!A5+30,"ddd")</f>
         <v/>
       </c>
@@ -2160,7 +2157,7 @@
       </c>
       <c r="D11" s="58" t="inlineStr">
         <is>
-          <t>Select **Beds!A4** and double-click the fill handle (column B is full, so Excel fills to row 39), or drag it down to **A39**.</t>
+          <t>Select Beds!A4 and double-click the fill handle (column B is full, so Excel fills to row 39), or drag it down to A39.</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -2174,7 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="141" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -2185,13 +2182,13 @@
           <t>On the Q15 Log sheet, A4 holds 07:00. Fill the yellow cells below it with a check time every 15 minutes, ending at 18:45. Use Home → Fill → Series, or the two-cell AutoFill pattern. The gray cell shows the latest time in column A.</t>
         </is>
       </c>
-      <c r="C12" s="64" t="n">
+      <c r="C12" s="63" t="n">
         <v>0.78125</v>
       </c>
       <c r="D12" s="58" t="inlineStr">
         <is>
-          <t>**Option A (Fill Series):** select **A4**, choose **Home → Fill → Series…**, pick **Columns** and **Linear**, type **0:15** as the Step value and **18:50** as the Stop value, then click **OK**.
-**Option B (AutoFill):** type **7:15** in A5, select A4:A5, and drag the fill handle down to **A51** (18:45).</t>
+          <t>Option A (Fill Series): select A4, choose Home → Fill → Series…, pick Columns and Linear, type 0:15 as the Step value and 18:50 as the Stop value, then click OK.
+Option B (AutoFill): type 7:15 in A5, select A4:A5, and drag the fill handle down to A51 (18:45).</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -2205,7 +2202,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
+    <row r="13" ht="111" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>9</t>
@@ -2221,9 +2218,9 @@
       </c>
       <c r="D13" s="58" t="inlineStr">
         <is>
-          <t>1. Click the first weekend cell in column O (the first Sat row), then **Ctrl+click** (Mac: **⌘+click**) every other Sat and Sun row.
-2. Type `FLOAT` (it appears in the last cell you clicked).
-3. Press **Ctrl + Enter** (Mac: **⌘ + Return**) to enter it in every selected cell at once.</t>
+          <t>1. Click the first weekend cell in column O (the first Sat row), then Ctrl+click (Mac: ⌘+click) every other Sat and Sun row.
+2. Type FLOAT (it appears in the last cell you clicked).
+3. Press Ctrl + Enter (Mac: ⌘ + Return) to enter it in every selected cell at once.</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -2237,7 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="171" customHeight="1">
+    <row r="14" ht="156" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
           <t>10</t>
@@ -2253,9 +2250,9 @@
       </c>
       <c r="D14" s="58" t="inlineStr">
         <is>
-          <t>1. In **Admissions!D2**, type `Rebecca R.` and press **Enter**.
-2. In **D3**, type `Russell Y.` and press **Enter**. If Excel shows a gray preview of the remaining labels while you type, you can press Enter to accept it.
-3. Otherwise press **Ctrl + E** (or choose **Data → Flash Fill**, on both Windows and Mac).
+          <t>1. In Admissions!D2, type Rebecca R. and press Enter.
+2. In D3, type Russell Y. and press Enter. If Excel shows a gray preview of the remaining labels while you type, you can press Enter to accept it.
+3. Otherwise press Ctrl + E (or choose Data → Flash Fill, on both Windows and Mac).
 4. Scan the results, and correct any row Flash Fill got wrong.</t>
         </is>
       </c>
@@ -2266,11 +2263,11 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Flash Fill studies your examples, finds the pattern ("the text after the comma, a space, the first letter, a period"), and applies it to every row. The first row needs help. In Richardson, Rebecca both names start with R, so Rebecca R. doesn't show *which* initial you want, and Flash Fill could turn Yilmaz, Russell into Russell R.. The second example, Russell Y., settles it. The results are typed-in values, not formulas, so they won't update if a name changes. A formula (Lesson 2.2) would. Many units use first name plus last initial on hallway whiteboards to protect patient privacy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="111" customHeight="1">
+          <t>Flash Fill studies your examples, finds the pattern ("the text after the comma, a space, the first letter, a period"), and applies it to every row. The first row needs help. In Richardson, Rebecca both names start with R, so Rebecca R. doesn't show which initial you want, and Flash Fill could turn Yilmaz, Russell into Russell R.. The second example, Russell Y., settles it. The results are typed-in values, not formulas, so they won't update if a name changes. A formula (Lesson 2.2) would. Many units use first name plus last initial on hallway whiteboards to protect patient privacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="96" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2286,18 +2283,18 @@
       </c>
       <c r="D15" s="58" t="inlineStr">
         <is>
-          <t>1. Select **Supplies!H4:H17** and press **Ctrl + C** (Mac: **⌘ + C**).
-2. Click **Order!D4**.
-3. Press **Ctrl + Alt + V** (Mac: **⌃ + ⌘ + V**) to open Paste Special, choose **Values**, and click **OK**. Or use **Home → Paste ▾ → Values (123)**.</t>
-        </is>
-      </c>
-      <c r="E15" cm="1" s="61">
+          <t>1. Select Supplies!H4:H17 and press Ctrl + C (Mac: ⌘ + C).
+2. Click Order!D4.
+3. Press Ctrl + Alt + V (Mac: ⌃ + ⌘ + V) to open Paste Special, choose Values, and click OK. Or use Home → Paste ▾ → Values (123).</t>
+        </is>
+      </c>
+      <c r="E15" cm="1" s="19">
         <f t="array" ref="E15">SUM(Supplies!H4:H17)</f>
         <v/>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>SuggestedOrder holds formulas such as =MAX(0,G4-F4). A normal paste copies the *formula*, and because its references are relative, it ends up pointing at the wrong cells on the Order sheet, so you see #VALUE! or wrong numbers. Paste Special → Values pastes only the *results*, which is what you want when the numbers must stay fixed or leave the workbook.</t>
+          <t>SuggestedOrder holds formulas such as =MAX(0,G4-F4). A normal paste copies the formula, and because its references are relative, it ends up pointing at the wrong cells on the Order sheet, so you see #VALUE! or wrong numbers. Paste Special → Values pastes only the results, which is what you want when the numbers must stay fixed or leave the workbook.</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2314,12 @@
       </c>
       <c r="D16" s="58" t="inlineStr">
         <is>
-          <t>1. Select **Schedule!A4:N35** and press **Ctrl + C** (Mac: **⌘ + C**).
-2. Click **Roster!A3**.
-3. Press **Ctrl + Alt + V** (Mac: **⌃ + ⌘ + V**), tick **Transpose**, and click **OK**. Or use **Home → Paste ▾ → Transpose**.</t>
-        </is>
-      </c>
-      <c r="E16" cm="1" s="61">
+          <t>1. Select Schedule!A4:N35 and press Ctrl + C (Mac: ⌘ + C).
+2. Click Roster!A3.
+3. Press Ctrl + Alt + V (Mac: ⌃ + ⌘ + V), tick Transpose, and click OK. Or use Home → Paste ▾ → Transpose.</t>
+        </is>
+      </c>
+      <c r="E16" cm="1" s="19">
         <f t="array" ref="E16">COUNTA(Schedule!I5:I35)</f>
         <v/>
       </c>
@@ -2332,7 +2329,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="171" customHeight="1">
+    <row r="17" ht="156" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>13</t>
@@ -2349,18 +2346,18 @@
       <c r="D17" s="58" t="inlineStr">
         <is>
           <t>1. Click any single cell on the Schedule sheet (so Excel searches the whole sheet).
-2. Press **Ctrl + H** (Mac: **⌃ + H**). Find what: `N`, Replace with: `N12`.
-3. Tick **Match entire cell contents** (click **Options &gt;&gt;** first if you can't see it). On a Mac the box is called **Find entire cells only**.
-4. Click **Replace All**. Excel reports how many replacements it made, which matches the gray cell.</t>
-        </is>
-      </c>
-      <c r="E17" cm="1" s="61">
+2. Press Ctrl + H (Mac: ⌃ + H). Find what: N, Replace with: N12.
+3. Tick Match entire cell contents (click Options &gt;&gt; first if you can't see it). On a Mac the box is called Find entire cells only.
+4. Click Replace All. Excel reports how many replacements it made, which matches the gray cell.</t>
+        </is>
+      </c>
+      <c r="E17" cm="1" s="19">
         <f t="array" ref="E17">COUNTIF(Schedule!C5:N35,"N")</f>
         <v/>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Without Match entire cell contents, Excel replaces the letter n *anywhere* in a cell, and it ignores capitals, so "Mon" would become "MoN12" and every name with an n would be damaged. With the option ticked, only cells containing exactly N change. Selecting just the code grid before Replace All is another safe approach, because Excel then searches only the selection.</t>
+          <t>Without Match entire cell contents, Excel replaces the letter n anywhere in a cell, and it ignores capitals, so "Mon" would become "MoN12" and every name with an n would be damaged. With the option ticked, only cells containing exactly N change. Selecting just the code grid before Replace All is another safe approach, because Excel then searches only the selection.</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2384,7 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2401,7 +2398,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Spoiler alert — try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution; column E is that same formula, live, proving it works.</t>
+          <t>Spoiler alert: try every task before reading this sheet. Column C is the value the Check column compares against. Column D is a sample solution, and column E recalculates a formula for it live, proving the answer.</t>
         </is>
       </c>
     </row>
@@ -2448,15 +2445,15 @@
           <t>Fill the date header C3:K3 with the next nine weekdays, skipping Saturdays and Sundays. The gray cell shows the date in K3.</t>
         </is>
       </c>
-      <c r="C5" s="62" t="n">
+      <c r="C5" s="61" t="n">
         <v>46038</v>
       </c>
       <c r="D5" s="58" t="inlineStr">
         <is>
-          <t>Select **B3:K3**, then choose **Home → Fill → Series…**: Rows, Type **Date**, Date unit **Weekday**, Step 1, and click **OK**. Or drag B3's fill handle to K3 and choose **Auto Fill Options → Fill Weekdays**.</t>
-        </is>
-      </c>
-      <c r="E5" cm="1" s="63">
+          <t>Select B3:K3, then choose Home → Fill → Series…: Rows, Type Date, Date unit Weekday, Step 1, and click OK. Or drag B3's fill handle to K3 and choose Auto Fill Options → Fill Weekdays.</t>
+        </is>
+      </c>
+      <c r="E5" cm="1" s="62">
         <f t="array" ref="E5">WORKDAY('Clinic Grid'!B3,9)</f>
         <v/>
       </c>
@@ -2466,7 +2463,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="81" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
           <t>B2</t>
@@ -2477,12 +2474,12 @@
           <t>Fill the time column A5:A39 with 15-minute slots after 08:00, ending at 16:45. The gray cell shows the latest time in column A.</t>
         </is>
       </c>
-      <c r="C6" s="64" t="n">
+      <c r="C6" s="63" t="n">
         <v>0.6979166666666666</v>
       </c>
       <c r="D6" s="58" t="inlineStr">
         <is>
-          <t>Select **A4**, choose **Home → Fill → Series…**: Columns, Linear, Step **0:15**, Stop **16:50**, and click **OK**. Or type 8:15 in A5, select both cells, and drag the fill handle to **A39**.</t>
+          <t>Select A4, choose Home → Fill → Series…: Columns, Linear, Step 0:15, Stop 16:50, and click OK. Or type 8:15 in A5, select both cells, and drag the fill handle to A39.</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2512,9 +2509,9 @@
       </c>
       <c r="D7" s="58" t="inlineStr">
         <is>
-          <t>1. Select **B4:K39**, type `Open`, and press **Ctrl + Enter** (Mac: **⌘ + Return**).
-2. Select **B20:K23** (12:00–12:45), type `Lunch`, and press **Ctrl + Enter**.
-3. Select **D24:D39**, Ctrl+drag (Mac: ⌘+drag) **I24:I39** (the two Wednesday afternoons), type `Admin`, and press **Ctrl + Enter**.</t>
+          <t>1. Select B4:K39, type Open, and press Ctrl + Enter (Mac: ⌘ + Return).
+2. Select B20:K23 (12:00–12:45), type Lunch, and press Ctrl + Enter.
+3. Select D24:D39, Ctrl+drag (Mac: ⌘+drag) I24:I39 (the two Wednesday afternoons), type Admin, and press Ctrl + Enter.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2544,9 +2541,9 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>1. Select **F24:F39**, then Ctrl+drag (Mac: ⌘+drag) **K24:K39**.
-2. Press **Ctrl + H** (Mac: **⌃ + H**). Find what: `Open`, Replace with: `Telehealth`. Tick **Match entire cell contents** for safety.
-3. Click **Replace All**. Because more than one cell is selected, Excel searches only the selection. (You can also do one Friday at a time and add the two counts.)</t>
+          <t>1. Select F24:F39, then Ctrl+drag (Mac: ⌘+drag) K24:K39.
+2. Press Ctrl + H (Mac: ⌃ + H). Find what: Open, Replace with: Telehealth. Tick Match entire cell contents for safety.
+3. Click Replace All. Because more than one cell is selected, Excel searches only the selection. (You can also do one Friday at a time and add the two counts.)</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2576,7 +2573,7 @@
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>Work it out: 36 rows × 10 days = 360 slots, minus 40 Lunch, 32 Admin, and 32 Telehealth = **256**. To confirm, click one cell on the Clinic Grid, press **Ctrl + F** (Mac: **⌃ + F**), type `Open`, tick **Match entire cell contents**, and click **Find All**. The dialog reports *"256 cell(s) found"*.</t>
+          <t>Work it out: 36 rows × 10 days = 360 slots, minus 40 Lunch, 32 Admin, and 32 Telehealth = 256. To confirm, click one cell on the Clinic Grid, press Ctrl + F (Mac: ⌃ + F), type Open, tick Match entire cell contents, and click Find All. The dialog reports "256 cell(s) found".</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">

--- a/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
+++ b/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C31"/>
+  <dimension ref="B2:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -811,7 +811,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Beginner  ·  about 40 minutes  ·  Bluestone Health System (fictional)</t>
+          <t>Beginner  ·  about 80 minutes  ·  Bluestone Health System (fictional)</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Enter and edit data efficiently (F2, Ctrl+Enter, Ctrl+D, Alt+Enter)</t>
+          <t>Enter and edit data efficiently (F2, Ctrl + Enter, Ctrl + D, Alt + Enter)</t>
         </is>
       </c>
     </row>
@@ -1030,46 +1030,70 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
+          <t>13 practice tasks, each with a Check cell.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
           <t>Admissions</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Data: 24 rows, in the Excel Table 'tblAdmissions'</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>About the data</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>A December 2025 rotating-RN schedule for Medical-Surgical 4 West, a registration record, a Q15 observation form, 4 West's bed list, supply room, and December admissions, plus a January 2026 clinic template for the bonus.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>A December 2025 rotating-RN schedule for Medical-Surgical 4 West, a registration record, a Q15 observation form, 4 West's bed list, supply room, and December admissions, plus a January 2026 clinic template for the bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>

--- a/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
+++ b/01-foundations/02-data-entry-autofill/1.2-data-entry-autofill.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -903,7 +903,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="33" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>2. Practice</t>
@@ -911,7 +911,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Go to the 'Practice' sheet. Type a formula or value into each yellow cell.</t>
+          <t>Go to the 'Practice' sheet. Type your answers for tasks 1–4 in its yellow cells. For tasks 5–13, do the work on the sheet each task names, and the task's gray cell on Practice reads it.</t>
         </is>
       </c>
     </row>
@@ -1042,58 +1042,142 @@
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Entries</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
+          <t>A registration record: what a clerk typed next to what Excel stored (tasks 1–2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="33" customHeight="1">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Data: 24 rows, in the Excel Table 'tblAdmissions'</t>
+          <t>4 West's December 2025 rotating-RN schedule. Fill the dates, day names, and weekend float column, then replace the N codes (tasks 5–6, 9, 13).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Beds</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>The bonus challenge (5 parts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1">
+          <t>4 West's 36 staffed beds. Fill the yellow Bed column (task 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>About the data</t>
+          <t>Q15 Log</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>A December 2025 rotating-RN schedule for Medical-Surgical 4 West, a registration record, a Q15 observation form, 4 West's bed list, supply room, and December admissions, plus a January 2026 clinic template for the bonus.</t>
+          <t>A Q15 safety observation form. Fill the 15-minute check times (task 8).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Data: 24 rows, in the Excel Table 'tblAdmissions'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Data: 14 rows, in the Excel Table 'tblSupplies'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>A supply requisition. Paste the restock quantities here as values (task 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Roster</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Empty. Paste the transposed schedule here, starting in A3 (task 12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>The bonus challenge (5 parts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Clinic Grid</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>The bonus appointment template you build. The Bonus sheet's gray cells read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>About the data</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>A December 2025 rotating-RN schedule for Medical-Surgical 4 West, a registration record, a Q15 observation form, 4 West's bed list, supply room, and December admissions, plus a January 2026 clinic template for the bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
           <t>Disclaimer</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>All people, places, and numbers are synthetic and fictional. Not clinical guidance.</t>
         </is>
@@ -1198,14 +1282,14 @@
     <row r="2" ht="79" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Julie Osei, MD, at the Primary Care Clinic in the Bluestone Outpatient Pavilion, needs an appointment template for the two weeks of Monday 01/05/2026 through Friday 01/16/2026. The clinic books 15-minute slots from 08:00 to 16:45 on weekdays only. Lunch (12:00–12:45) is blocked every day, Wednesday afternoons (13:00 onward) are admin time, and Friday afternoons become video visits. Build the whole grid on the Clinic Grid sheet with AutoFill, Fill Series, Ctrl+Enter, and Find &amp; Replace, without typing cell by cell. B3 (01/05/2026) and A4 (08:00) are filled in for you. The first four parts are checked by gray cells that read the Clinic Grid, so don't type over them. The last part has a yellow cell for your answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
+          <t>Julie Osei, MD, at the Primary Care Clinic in the Bluestone Outpatient Pavilion, needs an appointment template for the two weeks of Monday 01/05/2026 through Friday 01/16/2026. The clinic books 15-minute slots from 08:00 to 16:45 on weekdays only. Lunch (12:00–12:45) is blocked every day, Wednesday afternoons (13:00 onward) are admin time, and Friday afternoons become video visits. Build the whole grid on the Clinic Grid sheet with AutoFill, Fill Series, Ctrl + Enter, and Find &amp; Replace, without typing cell by cell. B3 (01/05/2026) and A4 (08:00) are filled in for you. The first four parts are checked by gray cells that read the Clinic Grid, so don't type over them. The last part has a yellow cell for your answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
+          <t>The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Bonus Key'.</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1384,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
+          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl + Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1416,7 +1500,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>Build the grid with AutoFill, Fill Series, Ctrl+Enter, and Find &amp; Replace. No typing cell by cell.</t>
+          <t>Build the grid with AutoFill, Fill Series, Ctrl + Enter, and Find &amp; Replace. No typing cell by cell.</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2110,7 @@
       </c>
       <c r="D6" s="58" t="inlineStr">
         <is>
-          <t>Select Entries!B7 and press Ctrl + Shift + ~ (Mac: ⌃ + Shift + ~), or choose Home → Number Format → General. Read the number, then press Ctrl + Z (Mac: ⌘ + Z) to put the date format back.</t>
+          <t>Select Entries!B7 and press Ctrl + Shift + ~ (Mac: Control + Shift + ~), or choose Home → Number Format → General. Read the number, then press Ctrl + Z (Mac: ⌘ + Z) to put the date format back.</t>
         </is>
       </c>
       <c r="E6" cm="1" s="60">
@@ -2089,7 +2173,7 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>Type Allergy: Penicillin, press Alt + Enter (Mac: ⌃ + ⌥ + Return), type Isolation: Contact, then press Enter.</t>
+          <t>Type Allergy: Penicillin, press Alt + Enter (Mac: Control + Option + Return), type Isolation: Contact, then press Enter.</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2203,7 +2287,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>On the Q15 Log sheet, A4 holds 07:00. Fill the yellow cells below it with a check time every 15 minutes, ending at 18:45. Use Home → Fill → Series, or the two-cell AutoFill pattern. The gray cell shows the latest time in column A.</t>
+          <t>On the Q15 Log sheet, A4 holds 07:00. Fill the yellow cells below it with a check time every 15 minutes, ending at 18:45. Use Home → Fill → Series…, or the two-cell AutoFill pattern. The gray cell shows the latest time in column A.</t>
         </is>
       </c>
       <c r="C12" s="63" t="n">
@@ -2234,7 +2318,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
+          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl + click (Mac: ⌘ + click) the weekend cells, type FLOAT, and press Ctrl + Enter (Mac: ⌘ + Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
         </is>
       </c>
       <c r="C13" s="57" t="n">
@@ -2242,7 +2326,7 @@
       </c>
       <c r="D13" s="58" t="inlineStr">
         <is>
-          <t>1. Click the first weekend cell in column O (the first Sat row), then Ctrl+click (Mac: ⌘+click) every other Sat and Sun row.
+          <t>1. Click the first weekend cell in column O (the first Sat row), then Ctrl + click (Mac: ⌘ + click) every other Sat and Sun row.
 2. Type FLOAT (it appears in the last cell you clicked).
 3. Press Ctrl + Enter (Mac: ⌘ + Return) to enter it in every selected cell at once.</t>
         </is>
@@ -2291,7 +2375,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="96" customHeight="1">
+    <row r="15" ht="111" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2309,7 +2393,7 @@
         <is>
           <t>1. Select Supplies!H4:H17 and press Ctrl + C (Mac: ⌘ + C).
 2. Click Order!D4.
-3. Press Ctrl + Alt + V (Mac: ⌃ + ⌘ + V) to open Paste Special, choose Values, and click OK. Or use Home → Paste ▾ → Values (123).</t>
+3. Press Ctrl + Alt + V (Mac: Control + ⌘ + V) to open Paste Special, choose Values, and click OK. Or use Home → Paste ▾ → Values (123).</t>
         </is>
       </c>
       <c r="E15" cm="1" s="19">
@@ -2340,7 +2424,7 @@
         <is>
           <t>1. Select Schedule!A4:N35 and press Ctrl + C (Mac: ⌘ + C).
 2. Click Roster!A3.
-3. Press Ctrl + Alt + V (Mac: ⌃ + ⌘ + V), tick Transpose, and click OK. Or use Home → Paste ▾ → Transpose.</t>
+3. Press Ctrl + Alt + V (Mac: Control + ⌘ + V), tick Transpose, and click OK. Or use Home → Paste ▾ → Transpose.</t>
         </is>
       </c>
       <c r="E16" cm="1" s="19">
@@ -2370,7 +2454,7 @@
       <c r="D17" s="58" t="inlineStr">
         <is>
           <t>1. Click any single cell on the Schedule sheet (so Excel searches the whole sheet).
-2. Press Ctrl + H (Mac: ⌃ + H). Find what: N, Replace with: N12.
+2. Press Ctrl + H (Mac: Control + H). Find what: N, Replace with: N12.
 3. Tick Match entire cell contents (click Options &gt;&gt; first if you can't see it). On a Mac the box is called Find entire cells only.
 4. Click Replace All. Excel reports how many replacements it made, which matches the gray cell.</t>
         </is>
@@ -2525,7 +2609,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl+Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
+          <t>Fill the whole grid B4:K39 with Open in one entry. Then type Lunch over the 12:00–12:45 rows for every day, and Admin over both Wednesday afternoons (13:00–16:45). Use one Ctrl + Enter for each step. The gray cell counts Lunch and Admin slots in the right places, minus any in the wrong place.</t>
         </is>
       </c>
       <c r="C7" s="57" t="n">
@@ -2535,7 +2619,7 @@
         <is>
           <t>1. Select B4:K39, type Open, and press Ctrl + Enter (Mac: ⌘ + Return).
 2. Select B20:K23 (12:00–12:45), type Lunch, and press Ctrl + Enter.
-3. Select D24:D39, Ctrl+drag (Mac: ⌘+drag) I24:I39 (the two Wednesday afternoons), type Admin, and press Ctrl + Enter.</t>
+3. Select D24:D39, Ctrl + drag (Mac: ⌘ + drag) I24:I39 (the two Wednesday afternoons), type Admin, and press Ctrl + Enter.</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2565,8 +2649,8 @@
       </c>
       <c r="D8" s="58" t="inlineStr">
         <is>
-          <t>1. Select F24:F39, then Ctrl+drag (Mac: ⌘+drag) K24:K39.
-2. Press Ctrl + H (Mac: ⌃ + H). Find what: Open, Replace with: Telehealth. Tick Match entire cell contents for safety.
+          <t>1. Select F24:F39, then Ctrl + drag (Mac: ⌘ + drag) K24:K39.
+2. Press Ctrl + H (Mac: Control + H). Find what: Open, Replace with: Telehealth. Tick Match entire cell contents for safety.
 3. Click Replace All. Because more than one cell is selected, Excel searches only the selection. (You can also do one Friday at a time and add the two counts.)</t>
         </is>
       </c>
@@ -2597,7 +2681,7 @@
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>Work it out: 36 rows × 10 days = 360 slots, minus 40 Lunch, 32 Admin, and 32 Telehealth = 256. To confirm, click one cell on the Clinic Grid, press Ctrl + F (Mac: ⌃ + F), type Open, tick Match entire cell contents, and click Find All. The dialog reports "256 cell(s) found".</t>
+          <t>Work it out: 36 rows × 10 days = 360 slots, minus 40 Lunch, 32 Admin, and 32 Telehealth = 256. To confirm, click one cell on the Clinic Grid, press Ctrl + F (Mac: Control + F), type Open, tick Match entire cell contents, and click Find All. The dialog reports "256 cell(s) found".</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -2647,14 +2731,14 @@
     <row r="2" ht="49" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Most tasks are done on the other sheets (Entries, Schedule, Beds, Q15 Log, Admissions, Supplies, Order, Roster). Type in the yellow cells here. A gray cell is a pre-filled formula that reads your work on another sheet, and its Check turns green when that work is right. Do the tasks in order, because the Schedule tasks build on each other.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
+          <t>Most tasks are done on the other sheets (Entries, Schedule, Beds, Q15 Log, Admissions, Supplies, Order, Roster). Type the answers for tasks 1–4 in the yellow cells on the Practice sheet. A gray cell is a pre-filled formula that reads your work on another sheet, and its Check turns green when that work is right. Do the tasks in order, because the Schedule tasks build on each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>Type a formula or value in each yellow cell. The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
+          <t>The Check column turns green when your answer matches. Stuck? Read the hint, then the lesson guide. Answers: right-click a sheet tab → Unhide… → 'Answer Key'.</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2938,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="51" customHeight="1">
+    <row r="13" ht="66" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>8</t>
@@ -2862,7 +2946,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>On the Q15 Log sheet, A4 holds 07:00. Fill the yellow cells below it with a check time every 15 minutes, ending at 18:45. Use Home → Fill → Series, or the two-cell AutoFill pattern. The gray cell shows the latest time in column A.</t>
+          <t>On the Q15 Log sheet, A4 holds 07:00. Fill the yellow cells below it with a check time every 15 minutes, ending at 18:45. Use Home → Fill → Series…, or the two-cell AutoFill pattern. The gray cell shows the latest time in column A.</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2887,7 +2971,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl+click (Mac: ⌘+click) the weekend cells, type FLOAT, and press Ctrl+Enter (Mac: ⌘+Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
+          <t>4 West gets one float-pool RN on every Saturday and Sunday. In the Weekend float column (O) of the Schedule sheet, put FLOAT in every weekend row and nowhere else, using a single entry: Ctrl + click (Mac: ⌘ + click) the weekend cells, type FLOAT, and press Ctrl + Enter (Mac: ⌘ + Return). The gray cell counts correctly placed FLOATs minus any entries on weekdays.</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
